--- a/Excel/EquipQualityConfig.xlsx
+++ b/Excel/EquipQualityConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>_Id</t>
   </si>
@@ -84,6 +89,9 @@
   </si>
   <si>
     <t>20,40,40,20</t>
+  </si>
+  <si>
+    <t>40,80,80,40</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1050,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E15"/>
+  <dimension ref="C3:E16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1182,6 +1190,17 @@
         <v>18</v>
       </c>
     </row>
+    <row r="16" spans="3:5">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">
